--- a/public/templates/forms/A-054-PatchManagementScheduleTrackingLog-FORM.xlsx
+++ b/public/templates/forms/A-054-PatchManagementScheduleTrackingLog-FORM.xlsx
@@ -3,13 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="22340" windowHeight="21660" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="22340" windowHeight="21660" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Patch Schedule" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Patch Tracking Log" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column Instructions" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Patch Schedule'!$10:$10</definedName>
+  </definedNames>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -17,7 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="11">
     <font>
       <name val="Aptos"/>
@@ -197,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -261,6 +266,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -613,7 +621,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
+    <row r="9" ht="34.7" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
           <t>« One row per system type. Set the cadence by criticality; note where CAD/RMS testing is required before deployment. Set Status from the dropdown. Requires the Master Asset Inventory and the Change Management Policy. »</t>
@@ -748,7 +756,6 @@
       <c r="B23" s="24" t="n"/>
       <c r="C23" s="13">
         <f>COUNTA(A11:A20)</f>
-        <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
@@ -760,7 +767,6 @@
       <c r="B24" s="24" t="n"/>
       <c r="C24" s="13">
         <f>COUNTIF(F11:F20,"Overdue")</f>
-        <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
@@ -772,7 +778,6 @@
       <c r="B25" s="24" t="n"/>
       <c r="C25" s="13">
         <f>COUNTIF(E11:E20,"&lt;"&amp;TODAY())</f>
-        <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
@@ -789,7 +794,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
+    <row r="29" ht="34.7" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
           <t>When a scheduled patch cycle is missed or a critical patch is overdue, the [IT support role] is notified within [24 hours] and the update is prioritized for the next window.</t>
@@ -940,7 +945,7 @@
       <c r="E46" s="12" t="n"/>
       <c r="F46" s="12" t="n"/>
     </row>
-    <row r="48" ht="30" customHeight="1">
+    <row r="48" ht="66.4" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Drafter's note (internal, delete before publishing): built as one artifact in two sheets, following the Backup Schedule &amp; Media Inventory precedent: the Patch Schedule sets cadence by system type and criticality; the Patch Tracking Log records what was applied. Kept in the Schedule type. DNS software is patched on the same schedule. Requires the Master Asset Inventory (system types) and the Change Management Policy; testing before deployment follows the Patch Testing Procedure. Agency-supplied values in brackets.</t>
@@ -985,7 +990,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -1013,14 +1018,14 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="34.7" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
           <t>« One row per patch or update applied. Record when, on what system, who approved it, and the outcome, including whether it was tested first. »</t>
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="34.7" customHeight="1">
       <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Date Applied</t>
@@ -1153,8 +1158,8 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -1187,7 +1192,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="29.75" customHeight="1">
+    <row r="3" ht="34.7" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Placeholder key:  [BRACKETED] = fill in   ·   « » = guidance to delete.  Classification, escalation, sign-off and revision history live on the Schedule tab.</t>
@@ -1223,7 +1228,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="34.7" customHeight="1">
       <c r="A7" s="20" t="inlineStr">
         <is>
           <t>System Type / Criticality</t>
@@ -1245,7 +1250,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
+    <row r="8" ht="50.5" customHeight="1">
       <c r="A8" s="20" t="inlineStr">
         <is>
           <t>Patch Source &amp; Test Requirement</t>
@@ -1289,7 +1294,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
+    <row r="10" ht="34.7" customHeight="1">
       <c r="A10" s="20" t="inlineStr">
         <is>
           <t>Owner (Role)</t>
@@ -1311,7 +1316,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="20" t="inlineStr">
         <is>
           <t>Next Due</t>
@@ -1327,10 +1332,8 @@
           <t>Required</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
+      <c r="D11" s="26">
+        <v>46113</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
@@ -1400,10 +1403,8 @@
           <t>Required</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
+      <c r="D16" s="26">
+        <v>46086</v>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1">
@@ -1545,7 +1546,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="34.7" customHeight="1">
       <c r="A26" s="20" t="inlineStr">
         <is>
           <t>Small (1–5, no in-house IT)</t>
@@ -1559,7 +1560,7 @@
       <c r="C26" s="23" t="n"/>
       <c r="D26" s="22" t="n"/>
     </row>
-    <row r="27">
+    <row r="27" ht="34.7" customHeight="1">
       <c r="A27" s="20" t="inlineStr">
         <is>
           <t>Medium (6–25, shared county IT)</t>
@@ -1573,7 +1574,7 @@
       <c r="C27" s="23" t="n"/>
       <c r="D27" s="22" t="n"/>
     </row>
-    <row r="28">
+    <row r="28" ht="34.7" customHeight="1">
       <c r="A28" s="20" t="inlineStr">
         <is>
           <t>Large (25+, dedicated IT/security)</t>
@@ -1599,6 +1600,6 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>